--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2024_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2024_nuble.xlsx
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:55</t>
+    <t xml:space="preserve">2026-09-09 21:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2024_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2024_nuble.xlsx
@@ -24,63 +24,63 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Chillán</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bulnes</t>
   </si>
   <si>
-    <t xml:space="preserve">Chillán</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chillán Viejo</t>
   </si>
   <si>
+    <t xml:space="preserve">El Carmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ignacio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yungay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quirihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
+    <t xml:space="preserve">Ninhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portezuelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treguaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Carlos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coihueco</t>
   </si>
   <si>
-    <t xml:space="preserve">El Carmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pemuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portezuelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quirihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Carlos</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
-    <t xml:space="preserve">San Ignacio</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
-    <t xml:space="preserve">Treguaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yungay</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:03</t>
+    <t xml:space="preserve">2026-09-18 10:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>78.57</v>
+        <v>79.55</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>79.55</v>
+        <v>78.57</v>
       </c>
     </row>
     <row r="4">
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>77.18</v>
+        <v>76.18</v>
       </c>
     </row>
     <row r="6">
@@ -534,7 +534,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>77.32</v>
+        <v>75.78</v>
       </c>
     </row>
     <row r="7">
@@ -542,7 +542,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>75.96</v>
+        <v>74.46</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>76.18</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="9">
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>77.32</v>
+        <v>75.9</v>
       </c>
     </row>
     <row r="10">
@@ -566,7 +566,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>75.78</v>
+        <v>80.83</v>
       </c>
     </row>
     <row r="11">
@@ -574,7 +574,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>74.46</v>
+        <v>81.1</v>
       </c>
     </row>
     <row r="12">
@@ -582,7 +582,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>78.56</v>
+        <v>77.18</v>
       </c>
     </row>
     <row r="13">
@@ -590,7 +590,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>76.84</v>
+        <v>77.32</v>
       </c>
     </row>
     <row r="14">
@@ -598,7 +598,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>81.1</v>
+        <v>77.32</v>
       </c>
     </row>
     <row r="15">
@@ -606,7 +606,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>78.45</v>
+        <v>78.56</v>
       </c>
     </row>
     <row r="16">
@@ -614,7 +614,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>70.83</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="17">
@@ -622,7 +622,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>75.9</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="18">
@@ -630,7 +630,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>76.96</v>
+        <v>75.96</v>
       </c>
     </row>
     <row r="19">
@@ -638,7 +638,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>80.5</v>
+        <v>70.83</v>
       </c>
     </row>
     <row r="20">
@@ -646,7 +646,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>80.83</v>
+        <v>76.96</v>
       </c>
     </row>
   </sheetData>
